--- a/misc/rectify_section6.xlsx
+++ b/misc/rectify_section6.xlsx
@@ -10184,7 +10184,7 @@
         <v>218</v>
       </c>
       <c r="B518" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C518" s="3" t="s">
         <v>421</v>
